--- a/ai/data/raw/Project_MovementSystem_QDatas.xlsx
+++ b/ai/data/raw/Project_MovementSystem_QDatas.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="671">
   <si>
     <t>id</t>
   </si>
@@ -46,6 +46,9 @@
     <t>answer</t>
   </si>
   <si>
+    <t>hint</t>
+  </si>
+  <si>
     <t>rationale</t>
   </si>
   <si>
@@ -73,7 +76,7 @@
     <t>neurocranium; kafa; os frontale; kafatası; alın; kemikleşmek; doğum</t>
   </si>
   <si>
-    <t>Doğumda 2 parça halinde olup 1–2 yaşlarında kemikleşerek tek parça hâline dönüşür.</t>
+    <t>Os Frontale, doğumda 2 parça halinde olup 1–2 yaşlarında kemikleşerek tek parça hâline dönüşür.</t>
   </si>
   <si>
     <t>{"options":["True","False"]}</t>
@@ -82,6 +85,9 @@
     <t>{"correct_index":1}</t>
   </si>
   <si>
+    <t>Kaç yaşında kemikleştiğine dikkat et.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre os frontale doğumda iki parçalıdır ve 5–6 yaşlarında tek kemik hâline gelir.</t>
   </si>
   <si>
@@ -106,6 +112,9 @@
     <t>{"options":["Os Temporale","Os Occipitale","Os Palatinum","Os Sphenoidale"]}</t>
   </si>
   <si>
+    <t>Omuriliğin kafatasına girdiği arka ve alt kısmı oluşturan kemiği düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, kafatası boşluğunun omurga kanalı ile bağlantısını sağlayan Foramen Magnum, Os Occipitale üzerindedir.</t>
   </si>
   <si>
@@ -124,6 +133,9 @@
     <t>{"correct_index":0}</t>
   </si>
   <si>
+    <t>Sella turcica denilen yapının hangi bez için özel bir yer oluşturduğunu düşün.</t>
+  </si>
+  <si>
     <t>os_parietale_tf_01</t>
   </si>
   <si>
@@ -136,6 +148,9 @@
     <t>Os Parietale kafatasının alt kısmında yer alır ve tek kemiktir.</t>
   </si>
   <si>
+    <t>Os parietalenin hem konumuna hem de çift mi tek mi olduğuna dikkat et.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre kafatasının üst yan duvarını oluşturur ve çift kemiktir.</t>
   </si>
   <si>
@@ -151,6 +166,9 @@
     <t>Os Temporale, kulakların ön üst bölümünde yer alır. İçinden dış kulak yolu geçer ve alt çene kemiği ile kafanın tek oynar eklemini oluşturur.</t>
   </si>
   <si>
+    <t>Şakak kemiğinin kulak bölgesi ve alt çene ile ilişkisini hatırla.</t>
+  </si>
+  <si>
     <t>os_ethmoidale_mcq_01</t>
   </si>
   <si>
@@ -166,6 +184,9 @@
     <t>{"options":["Kafatasının arka-alt kısmında yer alır ve foramen magnum’u içerir.","Kafanın ön kısmında, burun boşluğunun üst kısmında bulunur ve 2 adet sinüs içerir.","Kafatasının üst yan duvarını oluşturur ve çift kemiktir.","Kafanın ön kısmında yer alır ve orbitanın tavanını oluşturur."]}</t>
   </si>
   <si>
+    <t>Burun boşluğunun üst kısmında bulunan ve sinüs içeren kemiği düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, Os ethmoidale kafatası tabanında ve burun boşluğunun üst kısmında yer alan, kalbur görünümlü bir kemiktir. İki adet ethmoidal sinüs içerir ve concha nasalis superior ile media bu kemiğin uzantılarıdır.</t>
   </si>
   <si>
@@ -181,6 +202,9 @@
     <t>Burun bölmesinin üst kısmını oluşturan kemik Os Frontaledir.</t>
   </si>
   <si>
+    <t>Burun bölmesinin üst kısmını oluşturan kemiğin frontal değil farklı bir kemik olduğunu hatırla.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, burun bölmesinin üst kısmını oluşturan kemik Os Ethmoidaledir.</t>
   </si>
   <si>
@@ -202,6 +226,9 @@
     <t>{"correct_index":2}</t>
   </si>
   <si>
+    <t>Kafanın üst kısmında iki aynı kemik birbirine sutura sagittalis ile bağlanır.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, iki Os Parietale kafanın üst bölümünde birbiriyle (sutura sagittalis) eklem yapar.</t>
   </si>
   <si>
@@ -223,6 +250,9 @@
     <t>{"correct_index":3}</t>
   </si>
   <si>
+    <t>Yüz bölgesinde hem en büyük hem de en güçlü kemiği düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, yüz bölgesinin en büyük ve en kuvvetli kemiği Os Mandibula kemiğidir.</t>
   </si>
   <si>
@@ -244,6 +274,9 @@
     <t>{"options":["Os Mandibula - Os Maxilla","Os Mandibula - Os Palatinum","Os Maxilla - Os Mandibula","Os Palatinum - Os Mandibula"]}</t>
   </si>
   <si>
+    <t>Alt diş kemeri alt çenede, üst diş kemeri ise üst çenede bulunur.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, alt çene kemiği olan Os Mandibulada alt diş kemeri bulunurken üst çene kemiği olan Os Maxillada da üst diş kemeri bulunur.</t>
   </si>
   <si>
@@ -259,6 +292,9 @@
     <t>Os vomer, burun bölmesinin arka alt kısmını oluşturur.</t>
   </si>
   <si>
+    <t>Vomerin burun septumunun hangi bölümünü oluşturduğunu hatırla.</t>
+  </si>
+  <si>
     <t>os_maxilla_mcq_01</t>
   </si>
   <si>
@@ -274,6 +310,9 @@
     <t>{"options":["Ağız boşluğunun tavanının büyük kısmını oluşturur.","Göz çukurunun alt duvarını sınırlar.","Gövdesinde iki adet sinüs bulunur.","Kafatasının arka alt kısmında, foramen magnum çevresinde yer alır."]}</t>
   </si>
   <si>
+    <t>Foramen magnum ile ilişkili olan kemik yüz kemiği değil, kafatasının arka-alt kısmındaki kemiktir.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre bu ifade yanlıştır çünkü foramen magnum, kafatasının arka alt kısmında bulunan Os occipitale üzerinde yer alır; Os maxilla ise yüz bölgesinde, üst çeneyi oluşturur.</t>
   </si>
   <si>
@@ -289,6 +328,9 @@
     <t>Os zygomaticum, viscerocranium’un orta hattında yer alır ve burun boşluğunun tavanını oluşturur.</t>
   </si>
   <si>
+    <t>Elmacık kemiğinin orta hatta mı yoksa yüzün yan tarafında mı bulunduğunu düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre Os zygomaticum, viscerocranium’un yan tarafında yer alan çift bir kemiktir. Göz çukurunun alt-dış duvarını ve elmacık çıkıntısını oluşturur; burun boşluğunun tavanında bulunmaz.</t>
   </si>
   <si>
@@ -307,6 +349,9 @@
     <t>{"options":["Burun boşluğunun alt kısmında yer alır ve tek kemiktir.","Burun sırtının arka bölümünü oluşturur ve çift kemiktir.","Burun septumunun ön kısmını oluşturur ve düzensiz şekillidir.","Göz çukurunun dış duvarında bulunur ve elmacık çıkıntısını oluşturur."]}</t>
   </si>
   <si>
+    <t>Os nasale çift kemiktir ve burun sırtının bir bölümünü oluşturur.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre Os nasale, yüz iskeletine ait çift ve yassı bir kemiktir. Burun sırtının arka kısmını oluşturur ve orta hatta birbirine simetrik olarak birleşir.</t>
   </si>
   <si>
@@ -325,6 +370,9 @@
     <t>{"options":["Göz çukurunun dış yan duvarında yer alır ve elmacık kemiğiyle eklem yapar.","Yüz kemiklerinin en büyüklerinden biridir ve burun boşluğunun arka kısmını oluşturur.","Göz çukurunun iç yan duvarının ön bölümünde bulunur ve gözyaşı kanalıyla komşudur.","Kafatası tabanında yer alır ve ethmoidal sinüsleri barındırır."]}</t>
   </si>
   <si>
+    <t>Gözyaşı kanalıyla komşu olan küçük kemiğin orbita içinde hangi duvarda bulunduğunu düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre Os lacrimale, yüz kemiklerinin en küçük ve en ince olanıdır. Orbita’nın iç yan duvarının ön kısmında yer alır ve gözyaşı kanalı (ductus nasolacrimalis) ile komşudur.</t>
   </si>
   <si>
@@ -340,6 +388,9 @@
     <t>Os palatinum, maksilla ile birlikte sert damağın arka kısmını oluşturur ve ağız boşluğunun tavanının şekillenmesine katkı sağlar.</t>
   </si>
   <si>
+    <t>Sert damağın arka kısmını oluşturan kemikleri hatırla.</t>
+  </si>
+  <si>
     <t>concha_nasalis_inferior_tf_01</t>
   </si>
   <si>
@@ -352,6 +403,9 @@
     <t>Concha nasalis inferior, burun boşluğunun üst yan duvarında bulunur ve orta konkayı oluşturur.</t>
   </si>
   <si>
+    <t>Alt konkanın konumuna dikkat et; üstte değil daha aşağıdadır.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre Concha nasalis inferior, burun boşluğunun dış yan duvarında yer alır ve alttaki konkadır, orta konkayı oluşturmaz. Üst, orta ve alt olmak üzere üç konka bulunur; bunlardan yalnızca alt konka ayrı bir kemiktir.</t>
   </si>
   <si>
@@ -367,6 +421,9 @@
     <t>{"options":["Burun boşluğunun yan (lateral) duvarında yer alır.","Burun septumunu (vomer) oluşturan kemik çıkıntıdır.","Orbita (göz çukuru) medial duvarının ana parçasıdır.","Etmoid kemiğin uzantısı olup üst burun yolunu sınırlar."]}</t>
   </si>
   <si>
+    <t>Concha nasalis inferior burun boşluğunun septumunda değil yan duvarındadır.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre Concha nasalis inferior, burun boşluğunun dış yan duvarında yer alır.</t>
   </si>
   <si>
@@ -382,6 +439,9 @@
     <t>{"options":["Burun bölmesinin (septum nasi) arka-alt kısmını tek başına oluşturur.","Üst çene kemiği (maxilla) ile birlikte ağız boşluğunun tavanını, yani sert damağı oluşturur.","Göz çukurunun iç yan duvarının ön kısmında bulunan, yüz kemiklerinin en küçük kemiğidir.","Tek ve hareketli olan tek yüz kemiğidir."]}</t>
   </si>
   <si>
+    <t>Os palatinumun sert damağın oluşumuna katkısını hatırla.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre Os palatinum üst çene kemiği ile beraber ağız boşluğunun tavanını oluşturur.</t>
   </si>
   <si>
@@ -394,6 +454,9 @@
     <t>Os lacrimale, yüz kemiklerinin en küçüğü ve en incesidir.</t>
   </si>
   <si>
+    <t>Yüz kemikleri içinde en küçük ve en ince olan kemiği düşün.</t>
+  </si>
+  <si>
     <t>columna_vertebralis_mcq_01</t>
   </si>
   <si>
@@ -412,6 +475,9 @@
     <t>{"options":["Boyun ve Göğüs","Boyun ve Bel","Bel ve Sakrum","Göğüs ve Sakrum"]}</t>
   </si>
   <si>
+    <t>Lordozun boyun ve bel bölgelerinde görülen eğrilik olduğunu hatırla.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre lordoz yani omurganın arkaya doğru eğilmesi, boyun ve bel bölgesinde görülür.</t>
   </si>
   <si>
@@ -433,6 +499,9 @@
     <t>{"options":["Göğüs ve Bel","Boyun ve Sakrum","Göğüs ve Sakrum","Bel ve Boyun"]}</t>
   </si>
   <si>
+    <t>Kifozun göğüs ve sakrum bölgelerinde görüldüğünü düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre kifoz yani omurganın öne doğru eğilmesi, göğüs ve sakrum bölgesinde görülür.</t>
   </si>
   <si>
@@ -451,6 +520,9 @@
     <t>{"options":["Baş, boyun ve gövdenin ağırlığını taşır.","Başın ve gövdenin hareketlerini sağlar.","Omuriliği barındırır ve korur.","Kanda oksijen ve karbondioksit değişimini sağlayarak solunumu gerçekleştirir."]}</t>
   </si>
   <si>
+    <t>Omurganın görevleri destek, hareket ve koruma ile ilgilidir; solunum gaz değişimiyle değil.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre omurga taşıma, hareket ve koruma işlerini yapar.</t>
   </si>
   <si>
@@ -493,6 +565,9 @@
     <t>{"options":["Vertebrae cervicales ve Vertebrae coccygea","Vertebrae lumbales ve Vertebrae sacrale","Vertebrae sacrale ve Vertebrae coccygea","Vertebrae lumbales ve Vertebrae cervicales"]}</t>
   </si>
   <si>
+    <t>Yetişkinde kaynaşarak tek kemik hâline gelen omur gruplarını düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre yetişkinlerde sakrum (sağrı) ve koksiks (kuyruk sokumu) omurları kendi aralarında kaynaşıp birer kemiğe dönüşür.</t>
   </si>
   <si>
@@ -508,6 +583,9 @@
     <t>C1 omura atlas, C2 omura eksen (axis) adı verilir.</t>
   </si>
   <si>
+    <t>İlk iki boyun omurunun özel isimlerini hatırla.</t>
+  </si>
+  <si>
     <t>vertebrae_cervicales_tf_02</t>
   </si>
   <si>
@@ -517,6 +595,9 @@
     <t>C1 omurunun artkafa kemiği ve C2 omuru ile yaptığı eklemler kafanın hareketini sağlar.</t>
   </si>
   <si>
+    <t>Atlas ve axisin baş hareketlerindeki rolünü düşün.</t>
+  </si>
+  <si>
     <t>vertebrae_cervicales_mcq_01</t>
   </si>
   <si>
@@ -532,6 +613,9 @@
     <t>{"options":["5","7","4","12"]}</t>
   </si>
   <si>
+    <t>Boyun omurlarının sembolü C1’den başlar ve C7’ye kadar gider.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre 7 adet boyun omuru vardır ve C1-C7 sembolü ile gösterilirler.</t>
   </si>
   <si>
@@ -550,6 +634,9 @@
     <t>{"options":["4","7","12","5"]}</t>
   </si>
   <si>
+    <t>Göğüs omurları kaburga sayısıyla uyumlu olacak şekilde hatırlanabilir.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre 12 adet göğüs omuru vardır ve T1-T12 sembolü ile gösterilirler.</t>
   </si>
   <si>
@@ -565,6 +652,9 @@
     <t>Gövdesi en büyük ve en sağlam omurlar lumbal bölgededir.</t>
   </si>
   <si>
+    <t>Vücut ağırlığını en çok taşıyan omurların daha büyük ve sağlam olması beklenir.</t>
+  </si>
+  <si>
     <t>vertebrae_lumbales_mcq_01</t>
   </si>
   <si>
@@ -580,6 +670,9 @@
     <t>{"options":["4","5","7","12"]}</t>
   </si>
   <si>
+    <t>Bel omurlarının sayısını L1-L5 sembolünden hatırla.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre 5 adet boyun omuru vardır ve L1-L5 sembolü ile gösterilirler.</t>
   </si>
   <si>
@@ -598,6 +691,9 @@
     <t>{"options":["Boyun omurları","Göğüs omurları","Bel omurları","Sağrı omurları"]}</t>
   </si>
   <si>
+    <t>Ağırlık merkezinin S2 seviyesinin önüne denk geldiğini hatırla.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre vücudun ağırlık merkezi S2’nin 2-2,5 cm önüne denk gelir.</t>
   </si>
   <si>
@@ -616,6 +712,9 @@
     <t>{"options":["4","12","7","5"]}</t>
   </si>
   <si>
+    <t>Sağrı omurlarının sembolü S1’den başlar ve S5’e kadar gider.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre 5 adet sağrı omuru vardır ve S1-S5 sembolü ile gösterilirler.</t>
   </si>
   <si>
@@ -632,6 +731,9 @@
   </si>
   <si>
     <t>{"options":["12","7","4","5"]}</t>
+  </si>
+  <si>
+    <t>Kuyruk sokumu omurlarının sayısını Co1-Co4 sembolünden hatırla.</t>
   </si>
   <si>
     <t>Ders kitabına göre 4 adet kuyruk omuru vardır ve Co1-Co4 sembolü ile gösterilirler.</t>
@@ -657,6 +759,9 @@
 gövdesi/sternum sapı/hançersi çıkıntı"]}</t>
   </si>
   <si>
+    <t>Sternumun bölümlerini yukarıdan aşağıya sıralarken sap, gövde ve uç kısmı düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre göğüs tahtası kemiğinin üstteki kısmına sternum sapı (manubrium sterni), ortadaki kısmına sternum gövdesi (corpus sterni) ve uç kısmına ise hançersi çıkıntı (processus xiphoideus) denir.</t>
   </si>
   <si>
@@ -675,6 +780,9 @@
     <t>Hançersi çıkıntı, kaburgalarla eklem yapmaz.</t>
   </si>
   <si>
+    <t>Processus xiphoideusun kaburgalarla eklem yapıp yapmadığına dikkat et.</t>
+  </si>
+  <si>
     <t>ossa_costae_tf_01</t>
   </si>
   <si>
@@ -687,6 +795,9 @@
     <t>Yalancı kaburgaların kıkırdakları önce kendi aralarında birleşip 7’nci kaburganın kıkırdağına katılır ve sternumla dolaylı eklem yapar.</t>
   </si>
   <si>
+    <t>Yalancı kaburgaların hepsi aynı şekilde sternuma ulaşmaz; son iki çifte dikkat et.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre yalancı kaburgaların ilk 3 çiftinin kıkırdakları önce kendi aralarında birleşip 7’nci kaburganın kıkırdağına katılır ve sternumla dolaylı eklem yapar. Son 2 çift yalancı kaburga kasların içinde serbest olarak sonlanır.</t>
   </si>
   <si>
@@ -705,6 +816,9 @@
     <t>Vücutta en sık kırılan kemik köprücük kemiğidir.</t>
   </si>
   <si>
+    <t>Vücutta en sık kırılan kemiğin hangisi olduğunu düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabı s.61</t>
   </si>
   <si>
@@ -717,6 +831,9 @@
     <t>Kemikleşmeye ilk başlayan kemik köprücük kemiğidir.</t>
   </si>
   <si>
+    <t>Kemikleşmeye en erken başlayan kemiği hatırla.</t>
+  </si>
+  <si>
     <t>os_scapula_matching_01</t>
   </si>
   <si>
@@ -747,6 +864,9 @@
     <t>Os Humerus, üst ekstremitenin en uzun kemiğidir.</t>
   </si>
   <si>
+    <t>Üst ekstremitedeki en uzun kemiğin hangisi olduğunu düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabı s.62</t>
   </si>
   <si>
@@ -778,6 +898,9 @@
   </si>
   <si>
     <t>Dirsek kemiğinin humerus ile eklem yapan üst ucuna caput ulnae, bilek eklemine katılan kısma ise olecranon denir.</t>
+  </si>
+  <si>
+    <t>Olecranon ve caput ulnae isimlerinin hangi uçlara ait olduğunu karıştırma.</t>
   </si>
   <si>
     <t>Ders kitabına göre dirsek kemiğinin humerus ile eklem yapan üst ucuna olecranon (dirsek çıkıntısı), bilek eklemine katılan kısma ise caput ulnae (ulna başı) denir.</t>
@@ -796,6 +919,9 @@
 doğru döner.</t>
   </si>
   <si>
+    <t>Pronasyon sırasında radiusun ulna ile ilişkisini gözünde canlandır.</t>
+  </si>
+  <si>
     <t>os_radius_tf_02</t>
   </si>
   <si>
@@ -808,6 +934,9 @@
     <t>Anatomik duruşta os ulna ile os radius paraleldir.</t>
   </si>
   <si>
+    <t>Anatomik duruşta radius ve ulna çapraz değil yan yana uzanır.</t>
+  </si>
+  <si>
     <t>manus_matching_01</t>
   </si>
   <si>
@@ -841,6 +970,9 @@
     <t>Parmak kemiklerinin sayısı başparmakta 2 diğer parmaklarda 3’er tanedir.</t>
   </si>
   <si>
+    <t>Başparmağın falanks sayısını diğer parmaklarla karşılaştır.</t>
+  </si>
+  <si>
     <t>lower_extremity_tf_01</t>
   </si>
   <si>
@@ -856,6 +988,9 @@
     <t>Alt ekstremitede tek tarafta toplam 31 kemik bulunur.</t>
   </si>
   <si>
+    <t>Tek alt ekstremitedeki kemik sayısını toplam olarak düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabı s.65</t>
   </si>
   <si>
@@ -871,6 +1006,9 @@
     <t>Os coxa üç ayrı kemiğin birleşmesiyle oluşur.</t>
   </si>
   <si>
+    <t>Os coxanın tek kemik gibi görünse de gelişimsel olarak kaç parçadan oluştuğunu hatırla.</t>
+  </si>
+  <si>
     <t>Ders kitabı s.64</t>
   </si>
   <si>
@@ -886,6 +1024,9 @@
     <t>Os fibula diz ekleminin oluşumuna doğrudan katılır.</t>
   </si>
   <si>
+    <t>Fibulanın diz eklemine doğrudan katılıp katılmadığına dikkat et.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, fibula diz ekleminin oluşumuna doğrudan katılmaz.</t>
   </si>
   <si>
@@ -901,6 +1042,9 @@
     <t>Patella femur ile eklem yaparak diz eklemine katılır.</t>
   </si>
   <si>
+    <t>Patellanın diz ekleminde femurla ilişkisini düşün.</t>
+  </si>
+  <si>
     <t>os_talus_tf_01</t>
   </si>
   <si>
@@ -913,6 +1057,9 @@
     <t>Ayak bileğindeki en büyük kemik os talus’tur.</t>
   </si>
   <si>
+    <t>Ayak bölgesindeki en büyük kemiğin talus mu calcaneus mu olduğunu hatırla.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, ayak bileğindeki en büyük kemik os calcaneus’tur.</t>
   </si>
   <si>
@@ -925,6 +1072,9 @@
     <t>Os coxa, doğumdan itibaren tek kemik hâlindedir ve gelişim sürecinde üç parçaya ayrılır.</t>
   </si>
   <si>
+    <t>Os coxa doğumda tek kemik değildir; gelişim sırasını düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, os coxa başlangıçta üç ayrı kemikten (ilium, pubis, ischii) oluşur ve 15-16 yaşlarında kaynaşarak tek kemik hâline gelir.</t>
   </si>
   <si>
@@ -937,6 +1087,9 @@
     <t>Fibula kemiği diz ekleminin oluşumuna katılmaz ancak tibia ile eklem yapar.</t>
   </si>
   <si>
+    <t>Fibulanın tibia ile ilişkisini ve diz eklemine katılıp katılmadığını ayır.</t>
+  </si>
+  <si>
     <t>ossa_tarsi_tf_01</t>
   </si>
   <si>
@@ -949,6 +1102,9 @@
     <t>Her iki ayakta toplam 14 adet ossa tarsi bulunur.</t>
   </si>
   <si>
+    <t>Tek ayakta 7 tarsal kemik olduğunu hatırlarsan toplamı bulabilirsin.</t>
+  </si>
+  <si>
     <t>ossa_digitorum_pedis_tf01</t>
   </si>
   <si>
@@ -961,6 +1117,9 @@
     <t>Her iki alt ekstremitede bulunan toplam 62 kemiğin 28 tanesini ossa digitorum pedis oluşturur.</t>
   </si>
   <si>
+    <t>Bir ayakta 14 falanks varsa iki tarafta kaç tane olur diye düşün.</t>
+  </si>
+  <si>
     <t>lower_extremity_tf_02</t>
   </si>
   <si>
@@ -970,6 +1129,9 @@
     <t>Tek alt ekstremitede bulunan ossa metatarsi ve ossa digitorum pedis kemiklerinin toplam sayısı, ossa tarsi kemiklerinin sayısından fazladır.</t>
   </si>
   <si>
+    <t>Metatars ve falanks kemiklerinin toplamını tarsal kemiklerle karşılaştır.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, tek ayakta 5 ossa metatarsi ve 14 ossa digitorum pedis olmak üzere toplam 19 kemik bulunur. Ossa tarsi sayısı ise 7'dir. 19, 7'den fazladır.</t>
   </si>
   <si>
@@ -983,6 +1145,9 @@
   </si>
   <si>
     <t>{"options":["Os ilium","Os pubis","Os ischii","Os femur"]}</t>
+  </si>
+  <si>
+    <t>Os coxayı oluşturan kemikler pelvise aittir; uzun uyluk kemiği bunlardan biri değildir.</t>
   </si>
   <si>
     <t>Ders kitabına göre, os femur kalça kemiğini oluşturan kemikler arasında yer almaz.</t>
@@ -1007,6 +1172,9 @@
 </t>
   </si>
   <si>
+    <t>Femur başının kalça ekleminde oturduğu çukuru düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, femur başı acetabulum ile eklem yapar.</t>
   </si>
   <si>
@@ -1026,6 +1194,9 @@
 </t>
   </si>
   <si>
+    <t>Tibianın üstte diz eklemine hangi kemikle katıldığını hatırla.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, tibia üstte femur ile eklem yapar.</t>
   </si>
   <si>
@@ -1049,6 +1220,9 @@
 </t>
   </si>
   <si>
+    <t>Tek ayaktaki tarak kemiklerinin sayısını el tarak kemikleriyle benzetebilirsin.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, tek ayakta 5 metatars kemiği bulunur.</t>
   </si>
   <si>
@@ -1067,6 +1241,9 @@
     <t>{"options":["Toplam 14 kemik; başparmak 2, diğer parmaklar 3'er kemikten oluşur", "Toplam 15 kemik; tüm parmaklar 3'er kemikten oluşur", "Toplam 12 kemik; başparmak 2, diğer parmaklar 2'şer kemikten oluşur", "Toplam 16 kemik; başparmak 3, diğer parmaklar 3'er kemikten oluşur"]}</t>
   </si>
   <si>
+    <t>Başparmakta 2, diğer parmaklarda 3’er falanks bulunduğunu düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, tek ayakta toplam 14 falanks kemiği bulunur. Başparmak 2 kemikten, diğer dört parmak ise 3'er kemikten oluşur (2 + 12 = 14).</t>
   </si>
   <si>
@@ -1082,6 +1259,9 @@
     <t>{"options":["Tibia ve fibula", "Tibia ve femur", "Fibula ve calcaneus", "Femur ve tibia"]}</t>
   </si>
   <si>
+    <t>Ayak bileği ekleminde talus hangi bacak kemikleriyle temas eder, onu düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, talus tibia ve fibula ile eklem yaparak ayak bileği eklemini oluşturur.</t>
   </si>
   <si>
@@ -1097,6 +1277,9 @@
     <t>{"options":["Diz ekleminin oluşumuna doğrudan katılır", "Vücudun en uzun kemiğidir", "Tibia'ya destek sağlar ve diz eklemine katılmaz", "Femur başı ile eklem yapar"]}</t>
   </si>
   <si>
+    <t>Fibulanın ince bir destek kemiği olduğunu ve diz eklemine doğrudan katılmadığını hatırla.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, fibula tibia'ya destek sağlar; diz eklemine katılmaz.</t>
   </si>
   <si>
@@ -1115,6 +1298,9 @@
     <t>Syndesmosis eklemlerde kemik yüzleri arasında hiyalin kıkırdak bulunur.</t>
   </si>
   <si>
+    <t>Syndesmosis fibröz bir eklemdir; arada kıkırdak değil bağ dokusu bulunur.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, sindesmoz fibröz (lifli) bağ dokusu ile bağlanmış oynayamaz eklem tipidir; hiyalin kıkırdak bulunmaz.</t>
   </si>
   <si>
@@ -1133,6 +1319,9 @@
     <t>Sinovyal zar, eklem boşluğuna sinovyal sıvı salgılayarak eklem yüzlerinin beslenmesini ve sürtünmeye karşı korunmasını sağlar.</t>
   </si>
   <si>
+    <t>Sinovyal zarın görevi eklem sıvısı üretmek ve eklem yüzlerini korumaktır.</t>
+  </si>
+  <si>
     <t>Ders kitabı s.68</t>
   </si>
   <si>
@@ -1148,6 +1337,9 @@
     <t>Pronasyon, eklemin dışa doğru döndürülmesi olup lateral rotasyon ile aynı hareketi ifade eder.</t>
   </si>
   <si>
+    <t>Pronasyon ile lateral rotasyon aynı hareket değildir; ön kola odaklan.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, pronasyon radiusun ulna üzerine dönmesidir; lateral rotasyon ise eklemin dışa doğru döndürülmesidir. Aynı hareket değildir.</t>
   </si>
   <si>
@@ -1166,6 +1358,9 @@
     <t>Tek eksenli eklemler yalnızca bir eksen etrafında hareket yapabilir ve bu eklemler hem fleksiyon-ekstansiyon hem de rotasyon hareketlerini birlikte gerçekleştirebilir.</t>
   </si>
   <si>
+    <t>Tek eksenli eklemler yalnızca tek bir eksen çevresinde hareket eder.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, tek eksenli eklemler yalnızca bir eksen etrafında hareket yapar; birden fazla hareket tipini birlikte yapamaz.</t>
   </si>
   <si>
@@ -1184,6 +1379,9 @@
     <t>Diz eklemi femur, tibia, patella ve fibula kemikleri arasında oluşur.</t>
   </si>
   <si>
+    <t>Diz eklemine katılan kemikleri düşünürken fibulayı ayrıca sorgula.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, diz eklemi femur, tibia ve patella arasında oluşur; fibula diz eklemine katılmaz.</t>
   </si>
   <si>
@@ -1202,6 +1400,9 @@
     <t>Symphysis tipi yarı oynar eklemlerde eklem yüzleri arasında fibroz kıkırdak yapısında bir disk bulunur.</t>
   </si>
   <si>
+    <t>Symphysis tipinde eklem yüzleri arasında nasıl bir kıkırdak yapı bulunduğunu hatırla.</t>
+  </si>
+  <si>
     <t>sinovial_joint_tf_02</t>
   </si>
   <si>
@@ -1214,6 +1415,9 @@
     <t>Sinovyal eklem kapsülü tek katmanlı olup yalnızca fibröz zardan oluşur.</t>
   </si>
   <si>
+    <t>Sinovyal eklem kapsülü tek katmanlı değil, iki tabakalıdır.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, sinovyal eklem kapsülü iki katmandan oluşur: dışta fibröz zar, içte sinovyal zar bulunur.</t>
   </si>
   <si>
@@ -1229,6 +1433,9 @@
     <t>Çok eksenli eklemler yalnızca iki eksen etrafında hareket yapabilir ve sirkümdüksiyon gerçekleştiremez.</t>
   </si>
   <si>
+    <t>Çok eksenli eklemler sadece iki değil birden fazla eksende hareket edebilir.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, çok eksenli eklemler transvers, sagittal ve vertikal eksenlerde hareket yapabilir ve sirkümdüksiyon gerçekleştirebilir.</t>
   </si>
   <si>
@@ -1244,6 +1451,9 @@
     <t>Çıkık durumunda eklem yüzleri geçici olarak ayrılır ve kemikler kısa sürede anatomik konumlarına döner.</t>
   </si>
   <si>
+    <t>Çıkık ile burkulma arasındaki farkın kalıcılık durumunda olduğunu düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, çıkık eklemi oluşturan kemiklerin anatomik pozisyonlarını kaybederek eklem yüzlerinin kalıcı olarak ayrılması durumudur; geçici değildir.</t>
   </si>
   <si>
@@ -1259,6 +1469,9 @@
     <t>Burkulma, eklemi oluşturan kemiklerin anatomik pozisyonlarını kaybetmesi sonucu eklem yüzlerinin kalıcı olarak ayrılmasıdır.</t>
   </si>
   <si>
+    <t>Burkulmada ayrılma geçicidir, kalıcı ayrılma ise çıkıktır.</t>
+  </si>
+  <si>
     <t>ers kitabına göre, burkulma eklemi oluşturan kemiklerin ani olarak anatomik pozisyonlarını kaybederek eklem yüzlerinin geçici olarak ayrılmasıdır; kalıcı değildir</t>
   </si>
   <si>
@@ -1277,6 +1490,9 @@
     <t>{"options":["Sutura", "Gomphosis", "Sindesmoz", "Synchondrosis"]}</t>
   </si>
   <si>
+    <t>Fibröz eklemleri düşünürken kıkırdak içeren eklem tipini ele.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, synchondrosis yarı oynar (kartilaginöz) eklemdir; fibröz eklem değildir.</t>
   </si>
   <si>
@@ -1295,6 +1511,9 @@
     <t>{"options":["Kemiklerin doğrudan fibröz bağ ile bağlanması", "Eklem boşluğu ve sinovyal sıvı bulunması", "Eklem yüzleri arasında fibroz kıkırdak bulunması", "Hareket yeteneğinin olmaması"]}</t>
   </si>
   <si>
+    <t>Sinovyal eklemi ayıran temel özellik eklem boşluğu ve sinovyal sıvıdır.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, sinovyal eklemleri ayıran temel özellik eklem boşluğu ve sinovyal sıvı bulunmasıdır.</t>
   </si>
   <si>
@@ -1313,6 +1532,9 @@
     <t>{"options":["Ekstansiyon", "Abdüksiyon", "Fleksiyon", "Rotasyon"]}</t>
   </si>
   <si>
+    <t>Eklem açısının küçülmesi hangi hareketti, onu düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, eklem yüzleri arasındaki açının azalması fleksiyon olarak adlandırılır.</t>
   </si>
   <si>
@@ -1331,6 +1553,9 @@
     <t>{"options":["Fleksiyon ve ekstansiyon", "Fleksiyon, abdüksiyon ve rotasyon", "Abdüksiyon ve addüksiyon", "Rotasyon ve sirkümdüksiyon"]}</t>
   </si>
   <si>
+    <t>Tek eksenli eklemler en tipik olarak tek düzlemde bükülme-açılma yapar.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, tek eksenli eklemler yalnızca bir eksen etrafında hareket yapar; genellikle fleksiyon ve ekstansiyon gerçekleştirir.</t>
   </si>
   <si>
@@ -1349,6 +1574,9 @@
     <t>{"options":["Radiusun ulna üzerine dönmesi", "Eklemin dışa doğru döndürülmesi", "Ayağın içe doğru döndürülmesi", "Eklem yüzleri arasındaki açının artması"]}</t>
   </si>
   <si>
+    <t>Pronasyonda hareket eden kemik radius olup ulna üzerine döner.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, pronasyon radius kemiğinin ulna üzerine dönmesidir.</t>
   </si>
   <si>
@@ -1367,6 +1595,9 @@
     <t>{"options":["Hiyalin kıkırdak", "Fibroz kıkırdak disk", "Sinovyal sıvı", "Eklem boşluğu"]}</t>
   </si>
   <si>
+    <t>Synchondrosis tipinde eklem yüzleri arasında hangi tür kıkırdak olduğunu hatırla.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, synchondrosis tipi yarı oynar eklemlerde eklem yüzleri arasında hiyalin kıkırdak bulunur.</t>
   </si>
   <si>
@@ -1385,6 +1616,9 @@
     <t>{"options":["Fleksiyon, abdüksiyon, ekstansiyon ve addüksiyon", "Rotasyon ve inversiyon", "Ekstansiyon ve pronasyon", "Abdüksiyon ve eversiyon"]}</t>
   </si>
   <si>
+    <t>Sirkümdüksiyon tek bir hareket değil, birkaç hareketin ardışık birleşimidir.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, sirkümdüksiyon fleksiyon, abdüksiyon, ekstansiyon ve addüksiyon hareketlerinin dairesel şekilde ardışık tekrarıdır.</t>
   </si>
   <si>
@@ -1403,6 +1637,9 @@
     <t>{"options":["Transvers eksen – Fleksiyon/Ekstansiyon", "Sagittal eksen – Fleksiyon/Ekstansiyon", "Vertikal eksen – Abdüksiyon/Addüksiyon", "Transvers eksen – Rotasyon"]}</t>
   </si>
   <si>
+    <t>Fleksiyon ve ekstansiyonun hangi eksen etrafında gerçekleştiğini düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, transvers eksen etrafında fleksiyon ve ekstansiyon hareketi gerçekleşir.</t>
   </si>
   <si>
@@ -1421,6 +1658,9 @@
     <t>{"options":["Çıkıkta ayrılma kalıcıdır, burkulmada geçicidir", "Burkulmada kemikler kalıcı olarak ayrılır", "Çıkık yalnızca fibröz eklemlerde görülür", "Burkulma sinovyal sıvının azalmasıdır"]}</t>
   </si>
   <si>
+    <t>Çıkıkta ayrılma kalıcı, burkulmada ise geçicidir.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, çıkıkta eklem yüzleri kalıcı olarak ayrılır; burkulmada ayrılma geçicidir.</t>
   </si>
   <si>
@@ -1439,7 +1679,378 @@
     <t>{"options":["Vertikal eksen", "Transvers eksen", "Sagittal eksen", "Belirli bir eksen yoktur"]}</t>
   </si>
   <si>
+    <t>Pronasyon ve supinasyon rotasyon tipi hareketlerdir; rotasyonun eksenini düşün.</t>
+  </si>
+  <si>
     <t>Ders kitabına göre, pronasyon ve supinasyon vertikal eksen etrafında gerçekleşen rotasyon hareketleridir.</t>
+  </si>
+  <si>
+    <t>muscle_duty_mcq_01</t>
+  </si>
+  <si>
+    <t>Kasların Görevleri</t>
+  </si>
+  <si>
+    <t>Muscle</t>
+  </si>
+  <si>
+    <t>kas; görev; ısı; hareket; koruma</t>
+  </si>
+  <si>
+    <t>Aşağıdakilerden kaç tanesi doğrudur?
+1. Kaslar, kemik ve eklem yardımıyla hareketi sağlar.
+2. Kaslar kasılarak ısı üretir.
+3. İç organların etrafını sararak onları dış etkilerden korur.
+4. Kan dolaşımı, sindirim ve boşaltım gibi işlevleri gerçekleştirir.</t>
+  </si>
+  <si>
+    <t>{"options":["1", "2", "3", "4"]}</t>
+  </si>
+  <si>
+    <t>Dört maddenin de kasların temel görevleri arasında olup olmadığını tek tek kontrol et.</t>
+  </si>
+  <si>
+    <t>Ders kitabı s.72</t>
+  </si>
+  <si>
+    <t>muscle_mcq_01</t>
+  </si>
+  <si>
+    <t>Kas uçları</t>
+  </si>
+  <si>
+    <t>kas;  uç; origo; insertio</t>
+  </si>
+  <si>
+    <t>Aşağıdaki bilgilerin sırasıyla doğru veya yanlış olduğunu bulunuz.
+1. Kasın kemiklere yapışan başlangıç ucuna origo (orijin), sonlanma ucuna ise insertio (insersiyo) adı verilir.
+2. Orijin genellikle gövdeye yakın insersiyo ise gövdeye uzak uçtur.
+3. Kas kasıldığında hareketsiz veya az hareketli olan uç orijin, hareketli uç ise insersiyodur.</t>
+  </si>
+  <si>
+    <t>{"options":["Doğru-Yanlış-Doğru", "Doğru-Doğru-Yanlış", "Yanlış-Yanlış-Yanlış", "Doğru-Doğru-Doğru"]}</t>
+  </si>
+  <si>
+    <t>Origo daha sabit, insertio daha hareketli uç olarak düşünülür.</t>
+  </si>
+  <si>
+    <t>Ders kitabı s.73</t>
+  </si>
+  <si>
+    <t>muscle_type_matching_01</t>
+  </si>
+  <si>
+    <t>Kas çeşitleri</t>
+  </si>
+  <si>
+    <t>kas; çeşit; gövde şekli; baş sayısı; büyüklük; yaptıkları işlev</t>
+  </si>
+  <si>
+    <t>Aşağıdaki kas çeşitlerini eşleştiriniz.</t>
+  </si>
+  <si>
+    <t>{"left":["quadriceps", "trapezoid", "latissimus" , "supinator"], "right":["Gövde şekline göre", "Yaptıkları işleve göre", "Baş sayısına göre" , "Büyüklüklerine göre"], "shuffle_right":true}</t>
+  </si>
+  <si>
+    <t>{"pairs":[[0,2], [1,0], [2,3], [3,1]]}</t>
+  </si>
+  <si>
+    <t>muscle_matching_01</t>
+  </si>
+  <si>
+    <t>Yardımcı elemanlar</t>
+  </si>
+  <si>
+    <t>kas; yardımcı eleman; tendon; fascia; sinovyal; bursa synovialis; vagina synovialis tendinis</t>
+  </si>
+  <si>
+    <t>Aşağıdaki yardımcı elemanları özellikleri ile eşleştiriniz.</t>
+  </si>
+  <si>
+    <t>{"left":["Tendon", "Fascia", "Bursa synovialis" , "Vagina synovialis tendinis"], "right":["Kasların hem tek tek hem de toplu halde kasılmasına yardım eder.", "Kasların kemiklere tutunmasını sağlayan yapıdır.", "Kemik veya diğer sert kısımlardan geçen tendonları bir kılıf gibi saran, içinde sinovyal sıvı bulunan kesedir." , "Çıkıntılı kemik kısımlar ile kas ve tendon arasına koruyucu bir yastık gibi giren, içinde sinovyal sıvı bulunan kesedir."], "shuffle_right":true}</t>
+  </si>
+  <si>
+    <t>{"pairs":[[0,1], [1,0], [2,3], [3,2]]}</t>
+  </si>
+  <si>
+    <t>Ders kitabı s.75</t>
+  </si>
+  <si>
+    <t>head_muscle_mcq_01</t>
+  </si>
+  <si>
+    <t>Mimik/Çiğneme kasları</t>
+  </si>
+  <si>
+    <t>kas; yüz; kafa; mimik; çiğneme</t>
+  </si>
+  <si>
+    <t>Aşağıdaki kasların sırasıyla mimik mi çiğneme mi olduğunu bulunuz.
+1. M. Temporalis
+2. M. Orbicularis Oris
+3. M. Risorius
+4. M. Masseter</t>
+  </si>
+  <si>
+    <t>{"options":["Çiğneme-Mimik-Çiğneme-Mimik", "Mimik-Çiğneme-Mimik-Çiğneme", "Çiğneme-Mimik-Mimik-Çiğneme", "Mimik-Çiğneme-Çiğneme-Mimik"]}</t>
+  </si>
+  <si>
+    <t>M. temporalis ve M. masseter çiğneme; orbicularis oris ve risorius mimik kasıdır.</t>
+  </si>
+  <si>
+    <t>Ders kitabı s.76</t>
+  </si>
+  <si>
+    <t>neck_muscle_tf_01</t>
+  </si>
+  <si>
+    <t>SCM - T/F</t>
+  </si>
+  <si>
+    <t>kas; boyun; fleksiyon; kalın; yüzeysel</t>
+  </si>
+  <si>
+    <t>M. Sternocleidomastoideus, tek taraflı kasılınca başı kendi tarafına eğer, yüzü
+karşı tarafa baktırır. Çift taraflı kasılırsa başa fleksiyon yaptırır.</t>
+  </si>
+  <si>
+    <t>SCM’nin tek taraflı ve çift taraflı kasılmalarındaki etkileri ayrı ayrı düşün.</t>
+  </si>
+  <si>
+    <t>trunk_muscle_tf_01</t>
+  </si>
+  <si>
+    <t>M. Pectoralis - T/F</t>
+  </si>
+  <si>
+    <t>kas; göğüs; soluk</t>
+  </si>
+  <si>
+    <t>M. Pectoralis Minor, derin ve kuvvetli soluk almaya yardım eden göğüs kasıdır.</t>
+  </si>
+  <si>
+    <t>Derin ve kuvvetli soluk almaya yardım eden göğüs kasının major mu minor mu olduğuna dikkat et.</t>
+  </si>
+  <si>
+    <t>Ders kitabına göre, M. Pectoralis Major derin ve kuvvetli soluk almaya yardım eden göğüs kasıdır.</t>
+  </si>
+  <si>
+    <t>Ders kitabı s.77</t>
+  </si>
+  <si>
+    <t>trunk_muscle_tf_02</t>
+  </si>
+  <si>
+    <t>M. Subclavius - T/F</t>
+  </si>
+  <si>
+    <t>kas; göğüs; köprücük; koruma; damar; sinir</t>
+  </si>
+  <si>
+    <t>M. Subclavius, koltuk altı damar ve sinir ağını korur.</t>
+  </si>
+  <si>
+    <t>Köprücük kemiğinin altında bulunan bu kasın koruyucu görevini düşün.</t>
+  </si>
+  <si>
+    <t>trunk_muscle_mcq_01</t>
+  </si>
+  <si>
+    <t>Soluk alma kasları</t>
+  </si>
+  <si>
+    <t>kas; göğüs; derin; diyafram; soluk alma</t>
+  </si>
+  <si>
+    <t>Soluk almayı sağlayan esas kas hangisidir?</t>
+  </si>
+  <si>
+    <t>{"options":["Diaphragma", "M. Serratus Anterior", "M. Intercostales Externi", "M. Pectoralis Minor"]}</t>
+  </si>
+  <si>
+    <t>Soluk almanın ana motor gücü olan kubbe şeklindeki kası düşün.</t>
+  </si>
+  <si>
+    <t>Ders kitabına göre, Diyafragma soluk almayı sağlayan esas kastır.</t>
+  </si>
+  <si>
+    <t>Ders kitabı s.78</t>
+  </si>
+  <si>
+    <t>trunk_muscle_tf_03</t>
+  </si>
+  <si>
+    <t>Diyafram - T/F</t>
+  </si>
+  <si>
+    <t>kas; göğüs; derin; diyafram; kasılma; gevşeme</t>
+  </si>
+  <si>
+    <t>Diyafragma kasıldığında göğüs boşluğunu genişleterek soluk almayı sağlar. Gevşediğinde ise soluk verme gerçekleşir.</t>
+  </si>
+  <si>
+    <t>Diyafram kasıldığında aşağı iner ve göğüs boşluğunun hacmini artırır.</t>
+  </si>
+  <si>
+    <t>trunk_muscle_tf_04</t>
+  </si>
+  <si>
+    <t>M. Serratus Posterior Superior - T/F</t>
+  </si>
+  <si>
+    <t>kas; sırt; kaburga; kasılma; genişletme</t>
+  </si>
+  <si>
+    <t>M. Serratus Posterior Superior kası kasıldığı zaman kaburgaları yukarı doğru kaldırarak göğüs boşluğunu daraltır ve soluk vermeye yardımcı olur.</t>
+  </si>
+  <si>
+    <t>Superior kasın kaburgaları yukarı mı aşağı mı çektiğini ve bunun soluk alma mı verme mi sağladığını düşün.</t>
+  </si>
+  <si>
+    <t>Ders kitabına göre, M. Serratus Posterior Superior kası kasıldığı zaman kaburgaları yukarı doğru kaldırarak göğüs boşluğunu genişletir ve soluk almaya yardımcı olur.</t>
+  </si>
+  <si>
+    <t>Ders kitabı s.79</t>
+  </si>
+  <si>
+    <t>trunk_muscle_tf_05</t>
+  </si>
+  <si>
+    <t>M. Serratus Posterior Inferior - T/F</t>
+  </si>
+  <si>
+    <t>kas; sırt; kaburga; kasılma; daraltma</t>
+  </si>
+  <si>
+    <t>M. Serratus Posterior Inferior kası kasıldığı zaman kaburgaları aşağı doğru çekerek göğüs boşluğunu genişletir ve soluk almaya yardımcı olur.</t>
+  </si>
+  <si>
+    <t>Inferior kasın kaburgaları hangi yöne çektiğine ve göğüs boşluğunu genişletip genişletmediğine dikkat et.</t>
+  </si>
+  <si>
+    <t>Ders kitabına göre, M. Serratus Posterior Inferior kası kasıldığı zaman kaburgaları aşağı doğru çekerek göğüs boşluğunu daraltır ve soluk vermeye yardımcı olur.</t>
+  </si>
+  <si>
+    <t>muscle_duty_mcq_02</t>
+  </si>
+  <si>
+    <t>Karın kaslarının görevleri</t>
+  </si>
+  <si>
+    <t>kas; karın; görev; koruma; fleksiyon; rotasyon; dışkı; idrar; doğum</t>
+  </si>
+  <si>
+    <t>Aşağıdakilerden kaç tanesi karın kaslarının görevleridir?
+1. Karın boşluğundaki organları saran ve koruyan kaslardır.
+2. Organlara basınç uygulayarak dışkı ve idrar yapmaya yardımcı olur.
+3. Gövdenin fleksiyon ve rotasyonunu sağlar.
+4. Doğuma yardımcı olur.</t>
+  </si>
+  <si>
+    <t>Karın kaslarının görevlerini tek tek düşün; koruma, basınç oluşturma, hareket ve doğumla ilişkilerini kontrol et.</t>
+  </si>
+  <si>
+    <t>upper_extremity_muscle_tf_01</t>
+  </si>
+  <si>
+    <t>Omuz kasları rotasyon - T/F</t>
+  </si>
+  <si>
+    <t>kas; üst ekstremite; kol; rotasyon; iç; dış; omuz</t>
+  </si>
+  <si>
+    <t>M. Teres Major kası kola iç rotasyon yaptırır, M. Teres Minor kası ise kola dış rotasyon yaptırır.</t>
+  </si>
+  <si>
+    <t>Teres major ile teres minor kaslarının iç ve dış rotasyon görevlerini karşılaştır.</t>
+  </si>
+  <si>
+    <t>Ders kitabı s.80</t>
+  </si>
+  <si>
+    <t>upper_extremity_muscle_tf_02</t>
+  </si>
+  <si>
+    <t>Kol kası -T/F</t>
+  </si>
+  <si>
+    <t>kas; üst esktremite; kol; el; fleksör; ekstansör</t>
+  </si>
+  <si>
+    <t>Elin fleksör kasları ön kolun ön bölümünde, elin ekstansör kasları ise ön kolun arka bölümünde yer alır.</t>
+  </si>
+  <si>
+    <t>Fleksiyon yapan kaslar genellikle ön tarafta, ekstansiyon yapan kaslar ise arka tarafta bulunur.</t>
+  </si>
+  <si>
+    <t>Ders kitabı s.81</t>
+  </si>
+  <si>
+    <t>lower_extremity_muscle_mcq_01</t>
+  </si>
+  <si>
+    <t>Uyluk kasları</t>
+  </si>
+  <si>
+    <t>kas; alt ekstremite; uyluk; kalça; fleksör; ekstansör; abdüktör</t>
+  </si>
+  <si>
+    <t>Uyluğun en güçlü fleksör, ekstansör ve abdüktör kasları sırasıyla hangileridir?</t>
+  </si>
+  <si>
+    <t>{"options":["M. Gluteus Maximus-M. Iliopsoas-M. Gluteus Medius", "M. Iliopsoas-M. Gluteus Maximus-M. Gluteus Medius", "M. Gluteus Medius-M. Gluteus Maximus-M. Iliopsoas", "M. Iliopsoas-M. Gluteus Medius-M. Gluteus Maximus"]}</t>
+  </si>
+  <si>
+    <t>Kalça fleksiyonu, ekstansiyonu ve abdüksiyonu yapan en güçlü kasları sırasıyla düşün.</t>
+  </si>
+  <si>
+    <t>lower_extremity_muscle_mcq_02</t>
+  </si>
+  <si>
+    <t>Vücudun uzun kası</t>
+  </si>
+  <si>
+    <t>kas; alt ekstremite; uyluk; uzun</t>
+  </si>
+  <si>
+    <t>Vücudun en uzun kası hangisidir?</t>
+  </si>
+  <si>
+    <t>{"options":["M. Iliopsoas", "M. Rectus Abdominis", "M. Latissimus Dorsi", "M. Sartorius"]}</t>
+  </si>
+  <si>
+    <t>Leğen kemiğinden başlayıp uyluğun ön-iç tarafından geçerek tibianın üst kısmına uzanan uzun kası düşün.</t>
+  </si>
+  <si>
+    <t>Ders kitabına göre, leğen kemiğinden başlayıp ön iç yanından geçerek tibia kemiğinin üst ucunda sonlanan kas olan M. Sartorius vücudun en uzun kasıdır.</t>
+  </si>
+  <si>
+    <t>Ders kitabı s.82</t>
+  </si>
+  <si>
+    <t>lower_extremity_muscle_mcq_03</t>
+  </si>
+  <si>
+    <t>Aşil tendon</t>
+  </si>
+  <si>
+    <t>kas; alt ekstremite; baldır; aşil tendon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aşil tendonunu oluşturan kas hangisidir? </t>
+  </si>
+  <si>
+    <t>{"options":["M. Tibialis Posterior", "Hamstring Grubu Kaslar", "M. Triceps Surae", "M. Sartorius"]}</t>
+  </si>
+  <si>
+    <t>Baldırın arka kısmında bulunan ve topuk kemiğine Aşil tendonu ile bağlanan kas grubunu düşün.</t>
+  </si>
+  <si>
+    <t>Ders kitabına göre, M. Triceps Surae iki kas tibianın üst ucundan başlayıp aşil tendonunu oluşturduktan sonra topuk
+kemiğinde sonlanır.</t>
+  </si>
+  <si>
+    <t>Ders kitabı s.83</t>
   </si>
 </sst>
 </file>
@@ -1709,6 +2320,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="16.13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -1750,3365 +2364,4358 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" s="1">
         <v>30.0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1">
         <v>30.0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E5" s="1">
         <v>30.0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E6" s="1">
         <v>30.0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1">
         <v>30.0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>24</v>
+        <v>64</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E10" s="1">
         <v>30.0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E11" s="1">
         <v>30.0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>71</v>
+        <v>88</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E12" s="1">
         <v>30.0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="E13" s="1">
         <v>30.0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>71</v>
+        <v>100</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E14" s="1">
         <v>30.0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>71</v>
+        <v>106</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="E15" s="1">
         <v>30.0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>71</v>
+        <v>113</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E16" s="1">
         <v>30.0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>71</v>
+        <v>120</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="E17" s="1">
         <v>30.0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="E18" s="1">
         <v>30.0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>71</v>
+        <v>131</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="E19" s="1">
         <v>30.0</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>71</v>
+        <v>137</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="E20" s="1">
         <v>30.0</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>71</v>
+        <v>143</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="E21" s="1">
         <v>30.0</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="E22" s="1">
         <v>30.0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>134</v>
+        <v>155</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="E23" s="1">
         <v>30.0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>134</v>
+        <v>163</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="E24" s="1">
         <v>30.0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>134</v>
+        <v>170</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>154</v>
+        <v>177</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="E26" s="1">
         <v>30.0</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>154</v>
+        <v>185</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="E27" s="1">
         <v>30.0</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>154</v>
+        <v>39</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="E28" s="1">
         <v>30.0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>154</v>
+        <v>39</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="E29" s="1">
         <v>30.0</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>154</v>
+        <v>201</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="E30" s="1">
         <v>30.0</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="J30" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="N30" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="E31" s="1">
         <v>30.0</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>154</v>
+        <v>39</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="E32" s="1">
         <v>30.0</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>154</v>
+        <v>220</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="E33" s="1">
         <v>30.0</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>154</v>
+        <v>227</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="E34" s="1">
         <v>30.0</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>154</v>
+        <v>234</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="E35" s="1">
         <v>30.0</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>204</v>
+        <v>237</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>154</v>
+        <v>241</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="E36" s="1">
         <v>30.0</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>210</v>
+        <v>244</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>214</v>
+        <v>248</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="E37" s="1">
         <v>30.0</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>214</v>
+        <v>39</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>220</v>
+        <v>256</v>
       </c>
       <c r="E38" s="1">
         <v>30.0</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>221</v>
+        <v>257</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>214</v>
+        <v>260</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>224</v>
+        <v>261</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="E39" s="1">
         <v>30.0</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>227</v>
+        <v>264</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>229</v>
+        <v>39</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>230</v>
+        <v>268</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="E40" s="1">
         <v>30.0</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>231</v>
+        <v>269</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>229</v>
+        <v>39</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>233</v>
+        <v>272</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>234</v>
+        <v>273</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>236</v>
+        <v>275</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>237</v>
+        <v>276</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>229</v>
+        <v>277</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>239</v>
+        <v>278</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>240</v>
+        <v>279</v>
       </c>
       <c r="E42" s="1">
         <v>30.0</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>242</v>
+        <v>281</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>243</v>
+        <v>39</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>244</v>
+        <v>284</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>245</v>
+        <v>285</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>246</v>
+        <v>286</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>247</v>
+        <v>287</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>248</v>
+        <v>288</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>243</v>
+        <v>289</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>251</v>
+        <v>291</v>
       </c>
       <c r="E44" s="1">
         <v>30.0</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>252</v>
+        <v>292</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>253</v>
+        <v>293</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>254</v>
+        <v>294</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>243</v>
+        <v>295</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="E45" s="1">
         <v>30.0</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>243</v>
+        <v>39</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="E46" s="1">
         <v>30.0</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>261</v>
+        <v>303</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>262</v>
+        <v>304</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>243</v>
+        <v>39</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="H47" s="1" t="s">
-        <v>265</v>
+        <v>308</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>266</v>
+        <v>309</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>267</v>
+        <v>310</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>269</v>
+        <v>311</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>270</v>
+        <v>313</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>271</v>
+        <v>314</v>
       </c>
       <c r="E48" s="1">
         <v>30.0</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>272</v>
+        <v>315</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>273</v>
+        <v>316</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M48" s="1" t="s">
-        <v>269</v>
+        <v>39</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>274</v>
+        <v>318</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="E49" s="3">
         <v>30.0</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>277</v>
+        <v>321</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>278</v>
+        <v>322</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2" t="s">
-        <v>279</v>
+        <v>39</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>280</v>
+        <v>325</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>281</v>
+        <v>326</v>
       </c>
       <c r="E50" s="3">
         <v>30.0</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>282</v>
+        <v>327</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>283</v>
+        <v>328</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2" t="s">
-        <v>284</v>
+        <v>39</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>285</v>
+        <v>331</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>286</v>
+        <v>332</v>
       </c>
       <c r="E51" s="3">
         <v>30.0</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>287</v>
+        <v>333</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>288</v>
+        <v>334</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>289</v>
+        <v>23</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>284</v>
+        <v>336</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>290</v>
+        <v>337</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>291</v>
+        <v>338</v>
       </c>
       <c r="E52" s="3">
         <v>30.0</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>292</v>
+        <v>339</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>293</v>
+        <v>340</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2" t="s">
-        <v>284</v>
+        <v>39</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>294</v>
+        <v>342</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>295</v>
+        <v>343</v>
       </c>
       <c r="E53" s="3">
         <v>30.0</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>296</v>
+        <v>344</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>297</v>
+        <v>345</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>298</v>
+        <v>23</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>346</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>279</v>
+        <v>347</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>299</v>
+        <v>348</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>300</v>
+        <v>349</v>
       </c>
       <c r="E54" s="3">
         <v>30.0</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>282</v>
+        <v>327</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>301</v>
+        <v>350</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L54" s="2" t="s">
-        <v>302</v>
+        <v>23</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>351</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>284</v>
+        <v>352</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>303</v>
+        <v>353</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>304</v>
+        <v>354</v>
       </c>
       <c r="E55" s="3">
         <v>30.0</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>287</v>
+        <v>333</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>305</v>
+        <v>355</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L55" s="2"/>
-      <c r="M55" s="2" t="s">
-        <v>284</v>
+        <v>39</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>306</v>
+        <v>357</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>307</v>
+        <v>358</v>
       </c>
       <c r="E56" s="3">
         <v>30.0</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>308</v>
+        <v>359</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>309</v>
+        <v>360</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L56" s="2"/>
-      <c r="M56" s="2" t="s">
-        <v>279</v>
+        <v>39</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>310</v>
+        <v>362</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>311</v>
+        <v>363</v>
       </c>
       <c r="E57" s="3">
         <v>30.0</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>312</v>
+        <v>364</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L57" s="2"/>
-      <c r="M57" s="2" t="s">
-        <v>279</v>
+        <v>39</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>314</v>
+        <v>367</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="E58" s="3">
         <v>30.0</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>315</v>
+        <v>368</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>316</v>
+        <v>369</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L58" s="2" t="s">
-        <v>317</v>
+        <v>39</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>370</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>279</v>
+        <v>371</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="E59" s="3">
         <v>30.0</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>282</v>
+        <v>327</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>320</v>
+        <v>374</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>321</v>
+        <v>375</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L59" s="2" t="s">
-        <v>322</v>
+        <v>78</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>376</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>284</v>
+        <v>377</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>323</v>
+        <v>378</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>324</v>
+        <v>379</v>
       </c>
       <c r="E60" s="3">
         <v>30.0</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>325</v>
+        <v>380</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>326</v>
+        <v>381</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>327</v>
+        <v>382</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>329</v>
+        <v>383</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>284</v>
+        <v>385</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E61" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="N61" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="E61" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="J61" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="M61" s="2" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>336</v>
+        <v>393</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>337</v>
+        <v>394</v>
       </c>
       <c r="E62" s="3">
         <v>30.0</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>338</v>
+        <v>395</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>339</v>
+        <v>396</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>340</v>
+        <v>397</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>342</v>
+        <v>398</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>399</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>279</v>
+        <v>400</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>343</v>
+        <v>401</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>344</v>
+        <v>402</v>
       </c>
       <c r="E63" s="3">
         <v>30.0</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>345</v>
+        <v>403</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>346</v>
+        <v>404</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>347</v>
+        <v>405</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L63" s="2" t="s">
-        <v>348</v>
+        <v>39</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>406</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>279</v>
+        <v>407</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>349</v>
+        <v>408</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>350</v>
+        <v>409</v>
       </c>
       <c r="E64" s="3">
         <v>30.0</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>296</v>
+        <v>344</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>351</v>
+        <v>410</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>352</v>
+        <v>411</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>353</v>
+        <v>39</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>412</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>284</v>
+        <v>413</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>354</v>
+        <v>414</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>355</v>
+        <v>415</v>
       </c>
       <c r="E65" s="3">
         <v>30.0</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>287</v>
+        <v>333</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>357</v>
+        <v>417</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L65" s="2" t="s">
-        <v>358</v>
+        <v>70</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>418</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>284</v>
+        <v>419</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>359</v>
+        <v>420</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>360</v>
+        <v>421</v>
       </c>
       <c r="E66" s="3">
         <v>30.0</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>362</v>
+        <v>423</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>363</v>
+        <v>424</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>364</v>
+        <v>23</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>425</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>365</v>
+        <v>426</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>366</v>
+        <v>428</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>367</v>
+        <v>429</v>
       </c>
       <c r="E67" s="3">
         <v>30.0</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>368</v>
+        <v>430</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>369</v>
+        <v>431</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L67" s="2"/>
-      <c r="M67" s="2" t="s">
-        <v>370</v>
+        <v>39</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>371</v>
+        <v>434</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>372</v>
+        <v>435</v>
       </c>
       <c r="E68" s="3">
         <v>30.0</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>373</v>
+        <v>436</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>374</v>
+        <v>437</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>375</v>
+        <v>23</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>438</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>376</v>
+        <v>439</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>377</v>
+        <v>441</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>378</v>
+        <v>442</v>
       </c>
       <c r="E69" s="3">
         <v>30.0</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>379</v>
+        <v>443</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>380</v>
+        <v>444</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L69" s="2" t="s">
-        <v>381</v>
+        <v>23</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>382</v>
+        <v>446</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>383</v>
+        <v>448</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>384</v>
+        <v>449</v>
       </c>
       <c r="E70" s="3">
         <v>30.0</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>385</v>
+        <v>450</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>386</v>
+        <v>451</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L70" s="2" t="s">
-        <v>387</v>
+        <v>23</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>452</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>388</v>
+        <v>453</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>389</v>
+        <v>455</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>390</v>
+        <v>456</v>
       </c>
       <c r="E71" s="3">
         <v>30.0</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>391</v>
+        <v>457</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>392</v>
+        <v>458</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L71" s="2"/>
-      <c r="M71" s="2" t="s">
-        <v>365</v>
+        <v>39</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>393</v>
+        <v>460</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>394</v>
+        <v>461</v>
       </c>
       <c r="E72" s="3">
         <v>30.0</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>395</v>
+        <v>462</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>396</v>
+        <v>463</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>397</v>
+        <v>23</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>464</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>370</v>
+        <v>465</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>398</v>
+        <v>466</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>399</v>
+        <v>467</v>
       </c>
       <c r="E73" s="3">
         <v>30.0</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>400</v>
+        <v>468</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>401</v>
+        <v>469</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L73" s="2" t="s">
-        <v>402</v>
+        <v>23</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>470</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>382</v>
+        <v>471</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>403</v>
+        <v>472</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>404</v>
+        <v>473</v>
       </c>
       <c r="E74" s="3">
         <v>30.0</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>405</v>
+        <v>474</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>406</v>
+        <v>475</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L74" s="2" t="s">
-        <v>407</v>
+        <v>23</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>476</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>388</v>
+        <v>477</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>408</v>
+        <v>478</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>409</v>
+        <v>479</v>
       </c>
       <c r="E75" s="3">
         <v>30.0</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>410</v>
+        <v>480</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>411</v>
+        <v>481</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L75" s="2" t="s">
-        <v>412</v>
+        <v>23</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>482</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>388</v>
+        <v>483</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>413</v>
+        <v>484</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="E76" s="3">
         <v>30.0</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>415</v>
+        <v>486</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>416</v>
+        <v>487</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>417</v>
+        <v>488</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>418</v>
+        <v>78</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>489</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>365</v>
+        <v>490</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>419</v>
+        <v>491</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>420</v>
+        <v>492</v>
       </c>
       <c r="E77" s="3">
         <v>30.0</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>421</v>
+        <v>493</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>422</v>
+        <v>494</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>423</v>
+        <v>495</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>424</v>
+        <v>23</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>496</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>370</v>
+        <v>497</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>425</v>
+        <v>498</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>426</v>
+        <v>499</v>
       </c>
       <c r="E78" s="3">
         <v>30.0</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>427</v>
+        <v>500</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>428</v>
+        <v>501</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>429</v>
+        <v>502</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L78" s="2" t="s">
-        <v>430</v>
+        <v>70</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>503</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>376</v>
+        <v>504</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>431</v>
+        <v>505</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>432</v>
+        <v>506</v>
       </c>
       <c r="E79" s="3">
         <v>30.0</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>433</v>
+        <v>507</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>434</v>
+        <v>508</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>435</v>
+        <v>509</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L79" s="2" t="s">
-        <v>436</v>
+        <v>39</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>510</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>382</v>
+        <v>511</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>437</v>
+        <v>512</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>438</v>
+        <v>513</v>
       </c>
       <c r="E80" s="3">
         <v>30.0</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>439</v>
+        <v>514</v>
       </c>
       <c r="I80" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="N80" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>443</v>
+        <v>519</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>444</v>
+        <v>520</v>
       </c>
       <c r="E81" s="3">
         <v>30.0</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>445</v>
+        <v>521</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>446</v>
+        <v>522</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>447</v>
+        <v>523</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L81" s="2" t="s">
-        <v>448</v>
+        <v>39</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>524</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>365</v>
+        <v>525</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>449</v>
+        <v>526</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>450</v>
+        <v>527</v>
       </c>
       <c r="E82" s="3">
         <v>30.0</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>451</v>
+        <v>528</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>452</v>
+        <v>529</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>453</v>
+        <v>530</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L82" s="2" t="s">
-        <v>454</v>
+        <v>39</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>531</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>376</v>
+        <v>532</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>455</v>
+        <v>533</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>456</v>
+        <v>534</v>
       </c>
       <c r="E83" s="3">
         <v>30.0</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>457</v>
+        <v>535</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>458</v>
+        <v>536</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>459</v>
+        <v>537</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L83" s="2" t="s">
-        <v>460</v>
+        <v>39</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>538</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>376</v>
+        <v>539</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>461</v>
+        <v>540</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>462</v>
+        <v>541</v>
       </c>
       <c r="E84" s="3">
         <v>30.0</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>463</v>
+        <v>542</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>464</v>
+        <v>543</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>465</v>
+        <v>544</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L84" s="2" t="s">
-        <v>466</v>
+        <v>39</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>545</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>388</v>
+        <v>546</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>467</v>
+        <v>547</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>468</v>
+        <v>548</v>
       </c>
       <c r="E85" s="3">
         <v>30.0</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>469</v>
+        <v>549</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>470</v>
+        <v>550</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>471</v>
+        <v>551</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L85" s="2" t="s">
-        <v>472</v>
+        <v>39</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>552</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>376</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="86" ht="15.0" customHeight="1">
+      <c r="A86" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="E86" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="N86" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="87" ht="13.5" customHeight="1">
+      <c r="A87" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="E87" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="N87" s="1" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="N88" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="90" ht="14.25" customHeight="1">
+      <c r="A90" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="E90" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="N90" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="E91" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E92" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="N92" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E93" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E94" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="E95" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="E96" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="M96" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="E97" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="M97" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="98" ht="13.5" customHeight="1">
+      <c r="A98" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E98" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="E99" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="N99" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="E100" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="E101" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="E102" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="N102" s="1" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="E103" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="M103" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="N103" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="1"/>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/ai/data/raw/Project_MovementSystem_QDatas.xlsx
+++ b/ai/data/raw/Project_MovementSystem_QDatas.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="675">
   <si>
     <t>id</t>
   </si>
@@ -37,6 +37,9 @@
     <t>tags</t>
   </si>
   <si>
+    <t>level</t>
+  </si>
+  <si>
     <t>question_text</t>
   </si>
   <si>
@@ -76,6 +79,9 @@
     <t>neurocranium; kafa; os frontale; kafatası; alın; kemikleşmek; doğum</t>
   </si>
   <si>
+    <t>medium</t>
+  </si>
+  <si>
     <t>Os Frontale, doğumda 2 parça halinde olup 1–2 yaşlarında kemikleşerek tek parça hâline dönüşür.</t>
   </si>
   <si>
@@ -178,6 +184,9 @@
     <t>neurocranium; kafa; sinüs; kafatası; kalbur; burun</t>
   </si>
   <si>
+    <t>hard</t>
+  </si>
+  <si>
     <t>Aşağıdakilerden hangisi Os Ethmoidale ile ilgili doğru bir ifadedir?</t>
   </si>
   <si>
@@ -239,6 +248,9 @@
   </si>
   <si>
     <t>viscerocranium; yüz; yüz kemikleri; os mandibula; alt çene; büyük; kuvvet; çene; kafa</t>
+  </si>
+  <si>
+    <t>easy</t>
   </si>
   <si>
     <t>Yüz bölgesinin en büyük ve en kuvvetli kemiği hangisidir?</t>
@@ -2321,7 +2333,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.13"/>
+    <col customWidth="1" min="1" max="1" width="24.13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2367,4348 +2379,4657 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1">
         <v>30.0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4" s="1">
         <v>30.0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E5" s="1">
         <v>30.0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>26</v>
+        <v>48</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E6" s="1">
         <v>30.0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E8" s="1">
         <v>30.0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>26</v>
+        <v>67</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E10" s="1">
         <v>30.0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E11" s="1">
         <v>30.0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O11" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E12" s="1">
         <v>30.0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>81</v>
+        <v>41</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E13" s="1">
         <v>30.0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>81</v>
+        <v>104</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E14" s="1">
         <v>30.0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>81</v>
+        <v>110</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E15" s="1">
         <v>30.0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>81</v>
+        <v>117</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E16" s="1">
         <v>30.0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>81</v>
+        <v>124</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E17" s="1">
         <v>30.0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>81</v>
+        <v>41</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E18" s="1">
         <v>30.0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>81</v>
+        <v>135</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E19" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E19" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="I19" s="1" t="s">
-        <v>134</v>
+        <v>22</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>81</v>
+        <v>141</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E20" s="1">
         <v>30.0</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>140</v>
+        <v>22</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>23</v>
+        <v>145</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>142</v>
+        <v>25</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>81</v>
+        <v>147</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E21" s="1">
         <v>30.0</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>81</v>
+        <v>41</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E22" s="1">
         <v>30.0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>154</v>
+        <v>25</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E23" s="1">
         <v>30.0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="O23" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E24" s="1">
         <v>30.0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>167</v>
+        <v>22</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>156</v>
+        <v>174</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>175</v>
+        <v>22</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E26" s="1">
         <v>30.0</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E27" s="1">
         <v>30.0</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>22</v>
+        <v>193</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>178</v>
+        <v>41</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="E28" s="1">
         <v>30.0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>193</v>
+        <v>22</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>22</v>
+        <v>197</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>178</v>
+        <v>41</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E29" s="1">
         <v>30.0</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>198</v>
+        <v>79</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>23</v>
+        <v>203</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>178</v>
+        <v>205</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E30" s="1">
         <v>30.0</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>207</v>
+        <v>73</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>178</v>
+        <v>212</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E31" s="1">
         <v>30.0</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>22</v>
+        <v>216</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>178</v>
+        <v>41</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E32" s="1">
         <v>30.0</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>23</v>
+        <v>222</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>219</v>
+        <v>25</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>178</v>
+        <v>224</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E33" s="1">
         <v>30.0</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>224</v>
+        <v>57</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>78</v>
+        <v>229</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>178</v>
+        <v>231</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E34" s="1">
         <v>30.0</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>233</v>
+        <v>82</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>178</v>
+        <v>238</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E35" s="1">
         <v>30.0</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>238</v>
+        <v>79</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>70</v>
+        <v>243</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>240</v>
+        <v>73</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>178</v>
+        <v>245</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E36" s="1">
         <v>30.0</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>245</v>
+        <v>22</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>23</v>
+        <v>250</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>247</v>
+        <v>25</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E37" s="1">
         <v>30.0</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="O37" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E38" s="1">
         <v>30.0</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>258</v>
+        <v>57</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>22</v>
+        <v>262</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>259</v>
+        <v>25</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>249</v>
+        <v>264</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E39" s="1">
         <v>30.0</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>265</v>
+        <v>22</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>22</v>
+        <v>269</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>267</v>
+        <v>41</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E40" s="1">
         <v>30.0</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>270</v>
+        <v>22</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>22</v>
+        <v>274</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="O40" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>275</v>
+        <v>22</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>267</v>
+        <v>280</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E42" s="1">
         <v>30.0</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>281</v>
+        <v>79</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>22</v>
+        <v>285</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>283</v>
+        <v>41</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="I43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="O43" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E44" s="1">
         <v>30.0</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>293</v>
+        <v>57</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>22</v>
+        <v>297</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>294</v>
+        <v>25</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>283</v>
+        <v>299</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E45" s="1">
         <v>30.0</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>299</v>
+        <v>22</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>22</v>
+        <v>303</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>283</v>
+        <v>41</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E46" s="1">
         <v>30.0</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>304</v>
+        <v>22</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>22</v>
+        <v>308</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>283</v>
+        <v>41</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>309</v>
+        <v>22</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E48" s="1">
         <v>30.0</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="O48" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E49" s="3">
         <v>30.0</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>22</v>
+        <v>326</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2" t="s">
-        <v>324</v>
+        <v>24</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E50" s="3">
         <v>30.0</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>22</v>
+        <v>332</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2" t="s">
-        <v>330</v>
+        <v>24</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E51" s="3">
         <v>30.0</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="I51" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="O51" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="N51" s="2" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E52" s="3">
         <v>30.0</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>22</v>
+        <v>344</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L52" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2" t="s">
-        <v>330</v>
+        <v>24</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E53" s="3">
         <v>30.0</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>22</v>
+        <v>349</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>347</v>
+        <v>24</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>324</v>
+        <v>351</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E54" s="3">
         <v>30.0</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>350</v>
+        <v>331</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>22</v>
+        <v>354</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>352</v>
+        <v>24</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>330</v>
+        <v>356</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E55" s="3">
         <v>30.0</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>355</v>
+        <v>337</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="M55" s="2"/>
-      <c r="N55" s="2" t="s">
-        <v>330</v>
+        <v>359</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E56" s="3">
         <v>30.0</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>22</v>
+        <v>364</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2" t="s">
-        <v>324</v>
+        <v>24</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E57" s="3">
         <v>30.0</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>22</v>
+        <v>369</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2" t="s">
-        <v>324</v>
+        <v>24</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E58" s="3">
         <v>30.0</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>22</v>
+        <v>373</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>371</v>
+        <v>24</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>374</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>324</v>
+        <v>375</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E59" s="3">
         <v>30.0</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>374</v>
+        <v>331</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="M59" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>380</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>330</v>
+        <v>381</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E60" s="3">
         <v>30.0</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>388</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>330</v>
+        <v>389</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E61" s="3">
         <v>30.0</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="M61" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>395</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>330</v>
+        <v>396</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E62" s="3">
         <v>30.0</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="M62" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>403</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>324</v>
+        <v>404</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E63" s="3">
         <v>30.0</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="M63" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>324</v>
+        <v>411</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E64" s="3">
         <v>30.0</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>410</v>
+        <v>348</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L64" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>416</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>330</v>
+        <v>417</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E65" s="3">
         <v>30.0</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>416</v>
+        <v>337</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="M65" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>422</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>330</v>
+        <v>423</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E66" s="3">
         <v>30.0</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>22</v>
+        <v>428</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="M66" s="2" t="s">
-        <v>426</v>
+        <v>24</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>429</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E67" s="3">
         <v>30.0</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>22</v>
+        <v>435</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="M67" s="2"/>
-      <c r="N67" s="2" t="s">
-        <v>433</v>
+        <v>24</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E68" s="3">
         <v>30.0</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>22</v>
+        <v>441</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L68" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>439</v>
+        <v>24</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E69" s="3">
         <v>30.0</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>22</v>
+        <v>448</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="M69" s="2" t="s">
-        <v>446</v>
+        <v>24</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E70" s="3">
         <v>30.0</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>22</v>
+        <v>455</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L70" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="M70" s="2" t="s">
-        <v>453</v>
+        <v>24</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>456</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E71" s="3">
         <v>30.0</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>22</v>
+        <v>462</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="M71" s="2"/>
-      <c r="N71" s="2" t="s">
-        <v>427</v>
+        <v>24</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E72" s="3">
         <v>30.0</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>22</v>
+        <v>467</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L72" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="M72" s="2" t="s">
-        <v>465</v>
+        <v>24</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>468</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>433</v>
+        <v>469</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E73" s="3">
         <v>30.0</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>22</v>
+        <v>473</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L73" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="M73" s="2" t="s">
-        <v>471</v>
+        <v>24</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>474</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>447</v>
+        <v>475</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="E74" s="3">
         <v>30.0</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>22</v>
+        <v>479</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="M74" s="2" t="s">
-        <v>477</v>
+        <v>24</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>480</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>454</v>
+        <v>481</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E75" s="3">
         <v>30.0</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>22</v>
+        <v>485</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L75" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="M75" s="2" t="s">
-        <v>483</v>
+        <v>24</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>486</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>454</v>
+        <v>487</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E76" s="3">
         <v>30.0</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="L76" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>493</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>427</v>
+        <v>494</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E77" s="3">
         <v>30.0</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L77" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>500</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>433</v>
+        <v>501</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E78" s="3">
         <v>30.0</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L78" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="M78" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>507</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>440</v>
+        <v>508</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="E79" s="3">
         <v>30.0</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L79" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="M79" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>514</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>447</v>
+        <v>515</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="E80" s="3">
         <v>30.0</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L80" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>521</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>440</v>
+        <v>522</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E81" s="3">
         <v>30.0</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L81" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="M81" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>528</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>427</v>
+        <v>529</v>
+      </c>
+      <c r="O81" s="2" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="E82" s="3">
         <v>30.0</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L82" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="M82" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>535</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>440</v>
+        <v>536</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E83" s="3">
         <v>30.0</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L83" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>542</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>440</v>
+        <v>543</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="E84" s="3">
         <v>30.0</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L84" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="M84" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>549</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>454</v>
+        <v>550</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="E85" s="3">
         <v>30.0</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L85" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="M85" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>556</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>440</v>
+        <v>557</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="E86" s="1">
         <v>30.0</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>558</v>
+        <v>57</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>78</v>
+        <v>563</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="N86" s="1" t="s">
-        <v>561</v>
+        <v>82</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="87" ht="13.5" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="E87" s="1">
         <v>30.0</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>565</v>
+        <v>57</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>78</v>
+        <v>570</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="N87" s="1" t="s">
-        <v>568</v>
+        <v>82</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>572</v>
+        <v>22</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="N88" s="1" t="s">
-        <v>561</v>
+        <v>577</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="O88" s="1" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>578</v>
+        <v>22</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="N89" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="E90" s="1">
         <v>30.0</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>585</v>
+        <v>57</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>70</v>
+        <v>590</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="N90" s="1" t="s">
-        <v>588</v>
+        <v>73</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="E91" s="1">
         <v>30.0</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="I91" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="O91" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L91" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="N91" s="1" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E92" s="1">
         <v>30.0</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>597</v>
+        <v>22</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>22</v>
+        <v>601</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>598</v>
+        <v>25</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="E93" s="1">
         <v>30.0</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="I93" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="O93" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="J93" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="N93" s="1" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="E94" s="1">
         <v>30.0</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>609</v>
+        <v>22</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>39</v>
+        <v>614</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>611</v>
+        <v>41</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="E95" s="1">
         <v>30.0</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="I95" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="O95" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L95" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="N95" s="1" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="E96" s="1">
         <v>30.0</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>622</v>
+        <v>57</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>22</v>
+        <v>626</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>623</v>
+        <v>25</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
+      </c>
+      <c r="O96" s="1" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E97" s="1">
         <v>30.0</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="I97" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M97" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="O97" s="1" t="s">
         <v>629</v>
-      </c>
-      <c r="J97" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L97" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="M97" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="N97" s="1" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="98" ht="13.5" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="E98" s="1">
         <v>30.0</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>635</v>
+        <v>57</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>559</v>
+        <v>639</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>78</v>
+        <v>563</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="N98" s="1" t="s">
-        <v>625</v>
+        <v>82</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="O98" s="1" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E99" s="1">
         <v>30.0</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>640</v>
+        <v>22</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>22</v>
+        <v>644</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="N99" s="1" t="s">
-        <v>642</v>
+        <v>41</v>
+      </c>
+      <c r="M99" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="O99" s="1" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E100" s="1">
         <v>30.0</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>646</v>
+        <v>22</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>22</v>
+        <v>650</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="N100" s="1" t="s">
-        <v>648</v>
+        <v>41</v>
+      </c>
+      <c r="M100" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="O100" s="1" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="E101" s="1">
         <v>30.0</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="I101" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M101" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="O101" s="1" t="s">
         <v>652</v>
-      </c>
-      <c r="J101" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L101" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="N101" s="1" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E102" s="1">
         <v>30.0</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>658</v>
+        <v>22</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>78</v>
+        <v>663</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>660</v>
+        <v>82</v>
       </c>
       <c r="M102" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
+      </c>
+      <c r="O102" s="1" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="E103" s="1">
         <v>30.0</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>666</v>
+        <v>22</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>70</v>
+        <v>671</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>668</v>
+        <v>73</v>
       </c>
       <c r="M103" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>670</v>
+        <v>673</v>
+      </c>
+      <c r="O103" s="1" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="104">

--- a/ai/data/raw/Project_MovementSystem_QDatas.xlsx
+++ b/ai/data/raw/Project_MovementSystem_QDatas.xlsx
@@ -85,7 +85,7 @@
     <t>Os Frontale, doğumda 2 parça halinde olup 1–2 yaşlarında kemikleşerek tek parça hâline dönüşür.</t>
   </si>
   <si>
-    <t>{"options":["True","False"]}</t>
+    <t>{"options":["Doğru","Yanlış"]}</t>
   </si>
   <si>
     <t>{"correct_index":1}</t>
@@ -764,11 +764,7 @@
     <t>Göğüs tahtası kemiğini oluşturan 3 kısmın üstten alta doğru isimleri nelerdir?</t>
   </si>
   <si>
-    <t>{"options":["hançersi çıkıntı/sternum
-gövdesi/sternum sapı","sternum sapı/sternum
-gövdesi/hançersi çıkıntı","sternum
-gövdesi/hançersi çıkıntı/sternum sapı","sternum
-gövdesi/sternum sapı/hançersi çıkıntı"]}</t>
+    <t>{"options":["hançersi çıkıntı/sternum gövdesi/sternum sapı","sternum sapı/sternum gövdesi/hançersi çıkıntı","sternum gövdesi/hançersi çıkıntı/sternum sapı","sternum gövdesi/sternum sapı/hançersi çıkıntı"]}</t>
   </si>
   <si>
     <t>Sternumun bölümlerini yukarıdan aşağıya sıralarken sap, gövde ve uç kısmı düşün.</t>
@@ -927,8 +923,7 @@
     <t>antebrachium; ön kol; döner kemik; avuç içi</t>
   </si>
   <si>
-    <t>Öne uzatılan elin avuç içi aşağı çevrildiğinde os radius, ulnanın üzerine
-doğru döner.</t>
+    <t>Öne uzatılan elin avuç içi aşağı çevrildiğinde os radius, ulnanın üzerine doğru döner.</t>
   </si>
   <si>
     <t>Pronasyon sırasında radiusun ulna ile ilişkisini gözünde canlandır.</t>
@@ -1202,8 +1197,7 @@
     <t>Tibia'nın üst kısmı hangi kemik ile eklem yapar?</t>
   </si>
   <si>
-    <t xml:space="preserve">{"options":["Patella","Fibula","Femur","Talus"]}
-</t>
+    <t>{"options":["Patella","Fibula","Femur","Talus"]}</t>
   </si>
   <si>
     <t>Tibianın üstte diz eklemine hangi kemikle katıldığını hatırla.</t>
@@ -1224,8 +1218,7 @@
     <t>Tek ayakta kaç adet ossa metatarsi bulunur?</t>
   </si>
   <si>
-    <t xml:space="preserve">{"options":["5","7","10","14"]}
-</t>
+    <t>{"options":["5","7","10","14"]}</t>
   </si>
   <si>
     <t xml:space="preserve">{"correct_index":0}
@@ -1484,7 +1477,7 @@
     <t>Burkulmada ayrılma geçicidir, kalıcı ayrılma ise çıkıktır.</t>
   </si>
   <si>
-    <t>ers kitabına göre, burkulma eklemi oluşturan kemiklerin ani olarak anatomik pozisyonlarını kaybederek eklem yüzlerinin geçici olarak ayrılmasıdır; kalıcı değildir</t>
+    <t>Ders kitabına göre, burkulma eklemi oluşturan kemiklerin ani olarak anatomik pozisyonlarını kaybederek eklem yüzlerinin geçici olarak ayrılmasıdır; kalıcı değildir</t>
   </si>
   <si>
     <t>fibrous_joint_mcq_01</t>
@@ -1804,7 +1797,7 @@
 4. M. Masseter</t>
   </si>
   <si>
-    <t>{"options":["Çiğneme-Mimik-Çiğneme-Mimik", "Mimik-Çiğneme-Mimik-Çiğneme", "Çiğneme-Mimik-Mimik-Çiğneme", "Mimik-Çiğneme-Çiğneme-Mimik"]}</t>
+    <t>{"options":["Çiğneme-Mimik-Çiğneme-Mimik", "Mimik-Çiğneme-Mimik-Çiğneme", "Çiğneme-Mimik-Mimik Çiğneme", "Mimik-Çiğneme-Çiğneme Mimik"]}</t>
   </si>
   <si>
     <t>M. temporalis ve M. masseter çiğneme; orbicularis oris ve risorius mimik kasıdır.</t>
@@ -1822,8 +1815,7 @@
     <t>kas; boyun; fleksiyon; kalın; yüzeysel</t>
   </si>
   <si>
-    <t>M. Sternocleidomastoideus, tek taraflı kasılınca başı kendi tarafına eğer, yüzü
-karşı tarafa baktırır. Çift taraflı kasılırsa başa fleksiyon yaptırır.</t>
+    <t>M. Sternocleidomastoideus, tek taraflı kasılınca başı kendi tarafına eğer, yüzü karşı tarafa baktırır. Çift taraflı kasılırsa başa fleksiyon yaptırır.</t>
   </si>
   <si>
     <t>SCM’nin tek taraflı ve çift taraflı kasılmalarındaki etkileri ayrı ayrı düşün.</t>
@@ -2058,8 +2050,7 @@
     <t>Baldırın arka kısmında bulunan ve topuk kemiğine Aşil tendonu ile bağlanan kas grubunu düşün.</t>
   </si>
   <si>
-    <t>Ders kitabına göre, M. Triceps Surae iki kas tibianın üst ucundan başlayıp aşil tendonunu oluşturduktan sonra topuk
-kemiğinde sonlanır.</t>
+    <t>Ders kitabına göre, M. Triceps Surae iki kas tibianın üst ucundan başlayıp aşil tendonunu oluşturduktan sonra topuk kemiğinde sonlanır.</t>
   </si>
   <si>
     <t>Ders kitabı s.83</t>
@@ -4542,7 +4533,7 @@
       <c r="J49" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="K49" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L49" s="2" t="s">
@@ -4587,7 +4578,7 @@
       <c r="J50" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="K50" s="2" t="s">
+      <c r="K50" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L50" s="2" t="s">
@@ -4632,7 +4623,7 @@
       <c r="J51" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="K51" s="2" t="s">
+      <c r="K51" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L51" s="2" t="s">
@@ -4679,7 +4670,7 @@
       <c r="J52" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="K52" s="2" t="s">
+      <c r="K52" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L52" s="2" t="s">
@@ -4724,7 +4715,7 @@
       <c r="J53" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="K53" s="2" t="s">
+      <c r="K53" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L53" s="2" t="s">
@@ -4771,7 +4762,7 @@
       <c r="J54" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="K54" s="2" t="s">
+      <c r="K54" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L54" s="2" t="s">
@@ -4818,7 +4809,7 @@
       <c r="J55" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="K55" s="2" t="s">
+      <c r="K55" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L55" s="4" t="s">
@@ -4863,7 +4854,7 @@
       <c r="J56" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="K56" s="2" t="s">
+      <c r="K56" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L56" s="2" t="s">
@@ -4908,7 +4899,7 @@
       <c r="J57" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="K57" s="2" t="s">
+      <c r="K57" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L57" s="2" t="s">
@@ -4953,7 +4944,7 @@
       <c r="J58" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="K58" s="2" t="s">
+      <c r="K58" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L58" s="2" t="s">
@@ -5063,7 +5054,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="2" t="s">
         <v>390</v>
       </c>
@@ -5094,7 +5085,7 @@
       <c r="J61" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="K61" s="2" t="s">
+      <c r="K61" s="4" t="s">
         <v>394</v>
       </c>
       <c r="L61" s="2" t="s">
@@ -5141,7 +5132,7 @@
       <c r="J62" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="K62" s="2" t="s">
+      <c r="K62" s="4" t="s">
         <v>401</v>
       </c>
       <c r="L62" s="2" t="s">
@@ -5329,7 +5320,7 @@
       <c r="J66" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="K66" s="2" t="s">
+      <c r="K66" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L66" s="2" t="s">
@@ -5376,7 +5367,7 @@
       <c r="J67" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="K67" s="2" t="s">
+      <c r="K67" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L67" s="2" t="s">
@@ -5421,7 +5412,7 @@
       <c r="J68" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="K68" s="2" t="s">
+      <c r="K68" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L68" s="2" t="s">
@@ -5468,7 +5459,7 @@
       <c r="J69" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="K69" s="2" t="s">
+      <c r="K69" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L69" s="2" t="s">
@@ -5515,7 +5506,7 @@
       <c r="J70" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="K70" s="2" t="s">
+      <c r="K70" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L70" s="2" t="s">
@@ -5562,7 +5553,7 @@
       <c r="J71" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="K71" s="2" t="s">
+      <c r="K71" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L71" s="2" t="s">
@@ -5607,7 +5598,7 @@
       <c r="J72" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="K72" s="2" t="s">
+      <c r="K72" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L72" s="2" t="s">
@@ -5654,7 +5645,7 @@
       <c r="J73" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="K73" s="2" t="s">
+      <c r="K73" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L73" s="2" t="s">
@@ -5701,7 +5692,7 @@
       <c r="J74" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="K74" s="2" t="s">
+      <c r="K74" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L74" s="2" t="s">
@@ -5748,7 +5739,7 @@
       <c r="J75" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="K75" s="2" t="s">
+      <c r="K75" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L75" s="2" t="s">
@@ -5757,7 +5748,7 @@
       <c r="M75" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="N75" s="2" t="s">
+      <c r="N75" s="4" t="s">
         <v>487</v>
       </c>
       <c r="O75" s="2" t="s">

--- a/ai/data/raw/Project_MovementSystem_QDatas.xlsx
+++ b/ai/data/raw/Project_MovementSystem_QDatas.xlsx
@@ -556,7 +556,7 @@
     <t>{"left":["Vertebrae cervicales", "Vertebrae lumbales", "Vertebrae sacrale", "Vertebrae thoracicae", "Vertebrae coccygea"], "right":["T1-T12", "L1-L5", "C1-C7", "Co1-Co4", "S1-S5"], "shuffle_right":true}</t>
   </si>
   <si>
-    <t>{"pairs":[[0,2], [1,1], [2,4], [3,0], [4,3]]}</t>
+    <t>{"pairs":[{"leftIndex":0,"rightIndex":2},{"leftIndex":1,"rightIndex":1},{"leftIndex":2,"rightIndex":4},{"leftIndex":3,"rightIndex":0},{"leftIndex":4,"rightIndex":3}]}</t>
   </si>
   <si>
     <t>Ders kitabı s.59</t>
@@ -857,7 +857,7 @@
     <t>{"left":["Köprücük kemiği ile eklem yapan dış yana doğru uzanan çıkıntı", "Üst dış yanda öne doğru uzanan ve bazı kasların tutunduğu gagaya benzer çıkıntı", "Kol kemiğiyle eklem yapan üst dış kenarı"], "right":["cavitas glenoidalis", "acromion", "processus coracoideus"], "shuffle_right":true}</t>
   </si>
   <si>
-    <t>{"pairs":[[0,1], [1,2], [2,0]]}</t>
+    <t>{"pairs":[{"leftIndex":0,"rightIndex":1},{"leftIndex":1,"rightIndex":2},{"leftIndex":2,"rightIndex":0}]}</t>
   </si>
   <si>
     <t>os_humerus_tf_01</t>
@@ -893,7 +893,7 @@
     <t>{"left":["trochlea humeri", "caput humeri", "capitulum humeri"], "right":["Kürek kemiği ile eklem (omuz eklemi) yapar.", "İç yandaki dirsek kemiği ile eklem yapar.", "Dış yandaki döner kemikle eklem yapar."], "shuffle_right":true}</t>
   </si>
   <si>
-    <t>{"pairs":[[0,1], [1,0], [2,2]]}</t>
+    <t>{"pairs":[{"leftIndex":0,"rightIndex":1},{"leftIndex":1,"rightIndex":0},{"leftIndex":2,"rightIndex":2}]}</t>
   </si>
   <si>
     <t>os_ulna_tf_01</t>
@@ -959,7 +959,7 @@
     <t>{"left":["Ossa Carpi", "Ossa Metacarpi", "Ossa Digitorum Manus (Phalanges)"], "right":["4’erli iki sıra halinde 8 kısa kemik bulunur.", "Avuç içi ve el sırtının iskeletini oluşturan 5 uzun kemiktir.", "Beş parmakta toplam 14 kemik bulunur."], "shuffle_right":true}</t>
   </si>
   <si>
-    <t>{"pairs":[[0,0], [1,1], [2,2]]}</t>
+    <t>{"pairs":[{"leftIndex":0,"rightIndex":0},{"leftIndex":1,"rightIndex":1},{"leftIndex":2,"rightIndex":2}]}</t>
   </si>
   <si>
     <t>Ders kitabı s.63</t>
@@ -1757,7 +1757,7 @@
     <t>{"left":["quadriceps", "trapezoid", "latissimus" , "supinator"], "right":["Gövde şekline göre", "Yaptıkları işleve göre", "Baş sayısına göre" , "Büyüklüklerine göre"], "shuffle_right":true}</t>
   </si>
   <si>
-    <t>{"pairs":[[0,2], [1,0], [2,3], [3,1]]}</t>
+    <t>{"pairs":[{"leftIndex":0,"rightIndex":2},{"leftIndex":1,"rightIndex":0},{"leftIndex":2,"rightIndex":3},{"leftIndex":3,"rightIndex":1}]}</t>
   </si>
   <si>
     <t>muscle_matching_01</t>
@@ -1775,7 +1775,7 @@
     <t>{"left":["Tendon", "Fascia", "Bursa synovialis" , "Vagina synovialis tendinis"], "right":["Kasların hem tek tek hem de toplu halde kasılmasına yardım eder.", "Kasların kemiklere tutunmasını sağlayan yapıdır.", "Kemik veya diğer sert kısımlardan geçen tendonları bir kılıf gibi saran, içinde sinovyal sıvı bulunan kesedir." , "Çıkıntılı kemik kısımlar ile kas ve tendon arasına koruyucu bir yastık gibi giren, içinde sinovyal sıvı bulunan kesedir."], "shuffle_right":true}</t>
   </si>
   <si>
-    <t>{"pairs":[[0,1], [1,0], [2,3], [3,2]]}</t>
+    <t>{"pairs":[{"leftIndex":0,"rightIndex":1},{"leftIndex":1,"rightIndex":0},{"leftIndex":2,"rightIndex":3},{"leftIndex":3,"rightIndex":2}]}</t>
   </si>
   <si>
     <t>Ders kitabı s.75</t>
@@ -2325,6 +2325,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="24.13"/>
+    <col customWidth="1" min="12" max="12" width="14.63"/>
   </cols>
   <sheetData>
     <row r="1">
